--- a/Fuente.xlsx
+++ b/Fuente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bilbaoanalytics-my.sharepoint.com/personal/cristian_garcia_bilbaoanalytics_com/Documents/Proyecto CV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6174255-CBAB-400E-8F6E-E0C780A8264F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F9512AB5-45C2-48D0-9ADE-AE3A01B6BE58}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>index</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Bizagi</t>
+  </si>
+  <si>
+    <t>Ubicación</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4456ABE-8D8E-4529-A594-C5E3B52E8129}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -490,7 +493,7 @@
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,8 +506,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -518,7 +524,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -532,7 +538,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -546,7 +552,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -560,7 +566,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -574,7 +580,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -588,7 +594,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -602,7 +608,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -616,7 +622,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -630,7 +636,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -644,7 +650,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -658,7 +664,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -672,7 +678,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -686,7 +692,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>

--- a/Fuente.xlsx
+++ b/Fuente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bilbaoanalytics-my.sharepoint.com/personal/cristian_garcia_bilbaoanalytics_com/Documents/Proyecto CV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6174255-CBAB-400E-8F6E-E0C780A8264F}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EF4E94D-3FEE-4E07-94FB-91CC37A5BCD2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F9512AB5-45C2-48D0-9ADE-AE3A01B6BE58}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certificaciones!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certificaciones!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>index</t>
   </si>
@@ -114,6 +114,48 @@
   </si>
   <si>
     <t>Ubicación</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/1_Data_Analysis_with_python_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/BigData_el_impacto_de_los_datos_en_la_sociedad_actual_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/Certificado_Colsubsidio_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/Certificado_DataAnalytics_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/Introducci%C3%B3n_al_desarrollo_web_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/Modelamiento_de_procesos_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-estadistica-probabilidad_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-estrategiamarca_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-fidelizacion_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-hablar-en-publico_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-pensamiento-estrategico_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-python-cs%20(1)_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-python-fundamentos_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-scrum_page001.png?raw=true</t>
   </si>
 </sst>
 </file>
@@ -166,6 +208,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07FBB0FC-EB82-4743-9842-2F9293EA9578}" name="dimCertificaciones" displayName="dimCertificaciones" ref="A1:E15" totalsRowShown="0">
+  <autoFilter ref="A1:E15" xr:uid="{07FBB0FC-EB82-4743-9842-2F9293EA9578}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9573C57E-4280-49D2-BCB8-A07FE382734D}" name="index"/>
+    <tableColumn id="2" xr3:uid="{3D3E3766-AFB0-4DF1-AC1B-6A07E0177F66}" name="Nombre"/>
+    <tableColumn id="3" xr3:uid="{FC0F5FC6-C077-4ACE-938D-A8101D940632}" name="Escuela"/>
+    <tableColumn id="4" xr3:uid="{025569B5-5D97-450B-A6CA-AF59F5C8F9DD}" name="Año"/>
+    <tableColumn id="5" xr3:uid="{04F408FF-955D-48CD-AF2E-EFE41FF6AA70}" name="Ubicación"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,9 +544,10 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -523,6 +580,9 @@
       <c r="D2">
         <v>2025</v>
       </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -537,6 +597,9 @@
       <c r="D3">
         <v>2024</v>
       </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -551,6 +614,9 @@
       <c r="D4">
         <v>2024</v>
       </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -565,6 +631,9 @@
       <c r="D5">
         <v>2024</v>
       </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -579,6 +648,9 @@
       <c r="D6">
         <v>2024</v>
       </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -593,6 +665,9 @@
       <c r="D7">
         <v>2024</v>
       </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -607,6 +682,9 @@
       <c r="D8">
         <v>2024</v>
       </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -621,6 +699,9 @@
       <c r="D9">
         <v>2024</v>
       </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -635,6 +716,9 @@
       <c r="D10">
         <v>2023</v>
       </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -649,6 +733,9 @@
       <c r="D11">
         <v>2022</v>
       </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -663,6 +750,9 @@
       <c r="D12">
         <v>2022</v>
       </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -677,6 +767,9 @@
       <c r="D13">
         <v>2022</v>
       </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -691,6 +784,9 @@
       <c r="D14">
         <v>2022</v>
       </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -705,13 +801,14 @@
       <c r="D15">
         <v>2019</v>
       </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D15" xr:uid="{E4456ABE-8D8E-4529-A594-C5E3B52E8129}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
-      <sortCondition descending="1" ref="D1:D15"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Fuente.xlsx
+++ b/Fuente.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bilbaoanalytics-my.sharepoint.com/personal/cristian_garcia_bilbaoanalytics_com/Documents/Proyecto CV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EF4E94D-3FEE-4E07-94FB-91CC37A5BCD2}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{ABE2378A-CC56-4AD3-857F-B66704C2B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{044F883A-63CF-4D9F-BDCB-575143EE30ED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{F9512AB5-45C2-48D0-9ADE-AE3A01B6BE58}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="3" xr2:uid="{F9512AB5-45C2-48D0-9ADE-AE3A01B6BE58}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
+    <sheet name="Experiencia laboral" sheetId="2" r:id="rId2"/>
+    <sheet name="Herramientas" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certificaciones!$A$1:$E$15</definedName>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="118">
   <si>
     <t>index</t>
   </si>
@@ -156,16 +159,267 @@
   </si>
   <si>
     <t>https://github.com/IngBilbao/Proyecto-CV/blob/main/Certificaciones%20en%20im%C3%A1genes%20png/diploma-scrum_page001.png?raw=true</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>Logros clave</t>
+  </si>
+  <si>
+    <t>Global AI Interlink</t>
+  </si>
+  <si>
+    <t>Analista de Datos, Reporting y Estadísticas</t>
+  </si>
+  <si>
+    <t>Reducción del 50% en tiempos de procesamiento; reportes inteligentes con IA; modelos predictivos para datos operativos y financieros</t>
+  </si>
+  <si>
+    <t>Agrocampo SAS</t>
+  </si>
+  <si>
+    <t>Analista de Datos</t>
+  </si>
+  <si>
+    <t>Mar 2023 – Mar 2025</t>
+  </si>
+  <si>
+    <t>2 años</t>
+  </si>
+  <si>
+    <t>Reportes 300% más frecuentes (mensual → semanal); modelos de análisis para P&amp;G, compras y rentabilidad; reducción del 90% en errores operativos</t>
+  </si>
+  <si>
+    <t>Inversiones Alzate Ltda.</t>
+  </si>
+  <si>
+    <t>Analista de Gestión</t>
+  </si>
+  <si>
+    <t>Mar 2022 – Mar 2023</t>
+  </si>
+  <si>
+    <t>1 año</t>
+  </si>
+  <si>
+    <t>Automatización completa del ciclo de acuse de facturas; carga contable acelerada en 40%; cero errores en registro</t>
+  </si>
+  <si>
+    <t>Banco de Bogotá</t>
+  </si>
+  <si>
+    <t>Practicante Empresarial</t>
+  </si>
+  <si>
+    <t>Feb 2021 – Ago 2021</t>
+  </si>
+  <si>
+    <t>6 meses</t>
+  </si>
+  <si>
+    <t>Optimización de 4 procesos críticos; resultados publicados en artículo de investigación académica</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Abr 2025 – Feb 2026</t>
+  </si>
+  <si>
+    <t>Fecha inicio</t>
+  </si>
+  <si>
+    <t>Fecha fin</t>
+  </si>
+  <si>
+    <t>10 meses</t>
+  </si>
+  <si>
+    <t>Herramienta 1</t>
+  </si>
+  <si>
+    <t>Herramienta 2</t>
+  </si>
+  <si>
+    <t>Herramienta 3</t>
+  </si>
+  <si>
+    <t>Herramienta 4</t>
+  </si>
+  <si>
+    <t>Herramienta 5</t>
+  </si>
+  <si>
+    <t>Herramienta 6</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>Macros VBA</t>
+  </si>
+  <si>
+    <t>Power Query</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Power Apps</t>
+  </si>
+  <si>
+    <t>Looker studio</t>
+  </si>
+  <si>
+    <t>Herramienta</t>
+  </si>
+  <si>
+    <t>Power Automate</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>NotebookLM</t>
+  </si>
+  <si>
+    <t>Herramienta 7</t>
+  </si>
+  <si>
+    <t>Gsheets</t>
+  </si>
+  <si>
+    <t>Herramienta 8</t>
+  </si>
+  <si>
+    <t>Herramienta 9</t>
+  </si>
+  <si>
+    <t>ClickUp</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>JavaScript</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>Canva</t>
+  </si>
+  <si>
+    <t>https://www.aprender21.com/images/colaboradores/vba.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Microsoft_Office_Excel_%282025%E2%80%93present%29.svg/3840px-Microsoft_Office_Excel_%282025%E2%80%93present%29.svg.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cf/New_Power_BI_Logo.svg/960px-New_Power_BI_Logo.svg.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c3/Python-logo-notext.svg/1280px-Python-logo-notext.svg.png</t>
+  </si>
+  <si>
+    <t>https://symbols.getvecta.com/stencil_27/81_sql-database.712f6a994f.png</t>
+  </si>
+  <si>
+    <t>https://images.seeklogo.com/logo-png/61/2/looker-studio-logo-png_seeklogo-617989.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Microsoft_Power_Automate.svg/3840px-Microsoft_Power_Automate.svg.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/13/ChatGPT-Logo.png/1280px-ChatGPT-Logo.png</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/58/Claude-ai-icon.svg/3840px-Claude-ai-icon.svg.png</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>https://static.vecteezy.com/system/resources/previews/046/861/646/non_2x/gemini-icon-on-a-transparent-background-free-png.png</t>
+  </si>
+  <si>
+    <t>https://uxwing.com/wp-content/themes/uxwing/download/brands-and-social-media/notebooklm-icon.png</t>
+  </si>
+  <si>
+    <t>https://qualitytraining.be/content/uploads/2022/07/formation-google-sheet-belgique.png</t>
+  </si>
+  <si>
+    <t>https://www.northware.mx/wp-content/uploads/2022/09/northware-microsoft-power-apps-logo.png</t>
+  </si>
+  <si>
+    <t>https://clickup.com/images/for-se-page/clickup.png</t>
+  </si>
+  <si>
+    <t>https://cdn-icons-png.flaticon.com/512/5968/5968267.png</t>
+  </si>
+  <si>
+    <t>https://static.vecteezy.com/system/resources/previews/027/127/463/non_2x/javascript-logo-javascript-icon-transparent-free-png.png</t>
+  </si>
+  <si>
+    <t>https://cdn-icons-png.flaticon.com/512/25/25231.png</t>
+  </si>
+  <si>
+    <t>https://images.seeklogo.com/logo-png/65/2/canva-logo-png_seeklogo-653227.png</t>
+  </si>
+  <si>
+    <t>Apps Script</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/2f/Google_Apps_Script.svg/1280px-Google_Apps_Script.svg.png</t>
+  </si>
+  <si>
+    <t>https://awesome-astra.github.io/docs/img/microsoft-powerquery/microsoft-powerquery_logo.png</t>
+  </si>
+  <si>
+    <t>Proyecto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,13 +445,147 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="23">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm\-yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -219,6 +607,68 @@
     <tableColumn id="3" xr3:uid="{FC0F5FC6-C077-4ACE-938D-A8101D940632}" name="Escuela"/>
     <tableColumn id="4" xr3:uid="{025569B5-5D97-450B-A6CA-AF59F5C8F9DD}" name="Año"/>
     <tableColumn id="5" xr3:uid="{04F408FF-955D-48CD-AF2E-EFE41FF6AA70}" name="Ubicación"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{31378B61-5DFC-4297-A682-BE4B8CA7EB4A}" name="factExperiencia" displayName="factExperiencia" ref="A1:Q5" totalsRowShown="0" headerRowDxfId="22">
+  <autoFilter ref="A1:Q5" xr:uid="{31378B61-5DFC-4297-A682-BE4B8CA7EB4A}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{3F661225-2935-4509-BA08-1236076E041D}" name="Index" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{37DEB224-0700-4570-A3E0-E303A4836A06}" name="Empresa" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{3419E8B9-A538-42D0-96AA-D7D83A2BBE3D}" name="Cargo" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{F62A01EB-4DBD-40B8-9E3C-7633F41CFE1C}" name="Fecha inicio" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{AB7CC53C-8F11-4E29-AA22-38FEE67C0299}" name="Fecha fin" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{E5FBE995-8FC6-4DF8-9C33-A29EC0A81580}" name="Período" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{030B04DB-F5EF-4E7D-9A5B-E4FB39C78508}" name="Duración" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{FF32C991-61CF-4397-9504-771AFC65822A}" name="Logros clave" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{61CCE3FA-268C-4B6B-A5F7-78B74811434C}" name="Herramienta 1" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{BD103511-457D-4BCD-8330-F87C3D363F60}" name="Herramienta 2" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{038BA724-A6D7-459E-A8B2-E4B083CA61E5}" name="Herramienta 3" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{9637B967-CDA5-4066-A27B-9B00A6D4F402}" name="Herramienta 4"/>
+    <tableColumn id="13" xr3:uid="{7C627235-4216-4D0B-AF4E-878582F1D11B}" name="Herramienta 5"/>
+    <tableColumn id="14" xr3:uid="{3FDB6EDD-A900-47EB-ADAF-A5A741183871}" name="Herramienta 6"/>
+    <tableColumn id="15" xr3:uid="{A07CD9DE-DFD5-4001-A023-3680C6609AC8}" name="Herramienta 7"/>
+    <tableColumn id="16" xr3:uid="{1F8188AC-FA0E-4BAC-920F-2D11C3588A6B}" name="Herramienta 8"/>
+    <tableColumn id="17" xr3:uid="{1D4C1F6D-5C79-44DC-A78A-16772BE49918}" name="Herramienta 9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F0522939-42F0-477B-8261-5537BFE242A5}" name="dimHerramientas" displayName="dimHerramientas" ref="A1:B21" totalsRowShown="0">
+  <autoFilter ref="A1:B21" xr:uid="{F0522939-42F0-477B-8261-5537BFE242A5}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7048FCD5-C7B7-44B8-94FD-147A29BA4CCF}" name="Herramienta"/>
+    <tableColumn id="2" xr3:uid="{3234F48B-DDC5-472F-91AF-288F0431B4FA}" name="Ubicación"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{7ECA666A-0FB6-4622-9B56-EA3D365DE960}" name="factExperiencia5" displayName="factExperiencia5" ref="A1:P5" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:P5" xr:uid="{7ECA666A-0FB6-4622-9B56-EA3D365DE960}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{CD3D4B1A-0F1E-4F66-BDE8-DF6A8B101CB0}" name="Index" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{8C802F12-ABC8-4EBB-ABE6-F4E91C3CE083}" name="Proyecto" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{1BF72C54-E128-4221-8505-2393677BD0BE}" name="Fecha inicio" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{D60C175C-5B27-4FD1-B887-4B31C58017FD}" name="Fecha fin" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{8FA69078-CBD8-4FC8-813C-578661F40859}" name="Período" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{BCB5C8ED-46DD-4FBE-B83E-8A0E427F2720}" name="Duración" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{72BAC406-C206-43A1-A44D-C05CDF804A20}" name="Logros clave" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{9B24B62A-7BCD-48C6-AAC3-115827577412}" name="Herramienta 1" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{7CF90DEB-03F1-4BD9-8C20-6D8367724593}" name="Herramienta 2" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{DA95A3CA-843F-4D7C-9B7C-78FC42D0E596}" name="Herramienta 3" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{7B50D50C-CA5E-418D-AD28-21E57C6904CA}" name="Herramienta 4"/>
+    <tableColumn id="13" xr3:uid="{62896D98-B11A-4DF3-BF35-4EA88B15B246}" name="Herramienta 5"/>
+    <tableColumn id="14" xr3:uid="{349FA77A-7C04-4A05-A3E5-65AC4841311A}" name="Herramienta 6"/>
+    <tableColumn id="15" xr3:uid="{2A025C6B-AD38-4E8B-AFAA-7CEB3B696474}" name="Herramienta 7"/>
+    <tableColumn id="16" xr3:uid="{D6E5B358-5ABB-49F0-94CF-BFC6A499E24A}" name="Herramienta 8"/>
+    <tableColumn id="17" xr3:uid="{683236F2-EB7C-4B94-9537-D4E99E9879C9}" name="Herramienta 9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -811,4 +1261,607 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C79EBAC-E7A0-4599-86B6-1089F28710A3}">
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="53.28515625" customWidth="1"/>
+    <col min="9" max="17" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45748</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46054</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4">
+        <v>44986</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45717</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44621</v>
+      </c>
+      <c r="E4" s="4">
+        <v>44986</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="4">
+        <v>44228</v>
+      </c>
+      <c r="E5" s="4">
+        <v>44409</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49736504-6AA6-4E53-8624-CE8723AD5971}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75A8E8D-5FA0-4E9D-915B-6ED72C69C6EC}">
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.85546875" customWidth="1"/>
+    <col min="9" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>